--- a/forms/trg/Formulir_TRG_abdes.xlsx
+++ b/forms/trg/Formulir_TRG_abdes.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B29)</f>
+        <f>COUNTA(Anggota!B5:B30)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F29)</f>
+        <f>COUNTA(Anggota!F5:F30)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,33 +913,33 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Zulkharnaim, S.Pt., M.Si., IPM</t>
+          <t>Dr. Hasbi, S.Pt., M.Si</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="n"/>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Animal Reproductive Physiology</t>
+        </is>
+      </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-0277-6964</t>
+          <t>0000-0002-6069-2171</t>
         </is>
       </c>
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57190661295</t>
+          <t>58709078900</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Sahiruddin, S.Pt., M.Si., IPM., ASEAN Eng.</t>
+          <t>Dr. Ir. Zulkharnaim, S.Pt., M.Si., IPM</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -972,11 +972,15 @@
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="12" t="n"/>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-0277-6964</t>
+        </is>
+      </c>
       <c r="K6" s="12" t="n"/>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57200649915</t>
+          <t>57190661295</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -991,12 +995,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Muhammad Ihsan A. Dagong, S.Pt., M.Si</t>
+          <t>Dr. Ir. Sahiruddin, S.Pt., M.Si., IPM., ASEAN Eng.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1013,7 +1017,7 @@
       <c r="K7" s="12" t="n"/>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>57190659880</t>
+          <t>57200649915</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1028,12 +1032,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Syahriadi Kadir, M.Si</t>
+          <t>Dr. Muhammad Ihsan A. Dagong, S.Pt., M.Si</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1046,15 +1050,11 @@
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>0009-0006-2064-1309</t>
-        </is>
-      </c>
+      <c r="J8" s="12" t="n"/>
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>57217826834</t>
+          <t>57190659880</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Syahdar Baba, S.Pt., M.Si</t>
+          <t>Dr. Ir. Syahriadi Kadir, M.Si</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1087,11 +1087,15 @@
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>0009-0006-2064-1309</t>
+        </is>
+      </c>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>57190666581</t>
+          <t>57217826834</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1106,33 +1110,29 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Syahruddin Said, M.Agr.Sc., IPU., ASEAN Eng.</t>
+          <t>Prof. Dr. Syahdar Baba, S.Pt., M.Si</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>National Research and Innovation Agency</t>
-        </is>
-      </c>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="n"/>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-8681-4985</t>
-        </is>
-      </c>
+      <c r="J10" s="12" t="n"/>
       <c r="K10" s="12" t="n"/>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>57127585700</t>
+          <t>57190666581</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1147,33 +1147,33 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Dr. Sri Gustina, S.Pt., M.Si</t>
+          <t>Prof. Dr. Ir. Syahruddin Said, M.Agr.Sc., IPU., ASEAN Eng.</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>National Research and Innovation Agency</t>
+        </is>
+      </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-1466-4740</t>
+          <t>0000-0001-8681-4985</t>
         </is>
       </c>
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>57194022996</t>
+          <t>57127585700</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Dr. Erni Damayanti, S.Pt</t>
+          <t>Dr. Sri Gustina, S.Pt., M.Si</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1208,13 +1208,13 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-3028-2267</t>
+          <t>0000-0003-1466-4740</t>
         </is>
       </c>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>58112161100</t>
+          <t>57194022996</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Misbah Ahmad Ruhani, S.Pt., M.Si</t>
+          <t>Dr. Erni Damayanti, S.Pt</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1249,11 +1249,15 @@
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>0009-0003-8985-6197</t>
+          <t>0000-0003-3028-2267</t>
         </is>
       </c>
       <c r="K13" s="12" t="n"/>
-      <c r="L13" s="12" t="n"/>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>58112161100</t>
+        </is>
+      </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1266,12 +1270,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Siti Nuraisyah Hamsir, S.Pt</t>
+          <t>Muhammad Misbah Ahmad Ruhani, S.Pt., M.Si</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1286,7 +1290,7 @@
       <c r="I14" s="12" t="n"/>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>0009-0003-4584-7117</t>
+          <t>0009-0003-8985-6197</t>
         </is>
       </c>
       <c r="K14" s="12" t="n"/>
@@ -1303,12 +1307,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Yuni Sartika, S.Pt., M.Si</t>
+          <t>Siti Nuraisyah Hamsir, S.Pt</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1323,7 +1327,7 @@
       <c r="I15" s="12" t="n"/>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>0009-0006-1245-4992</t>
+          <t>0009-0003-4584-7117</t>
         </is>
       </c>
       <c r="K15" s="12" t="n"/>
@@ -1340,12 +1344,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Abd. Mutalib</t>
+          <t>Yuni Sartika, S.Pt., M.Si</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1358,7 +1362,11 @@
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
       <c r="I16" s="12" t="n"/>
-      <c r="J16" s="12" t="n"/>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>0009-0006-1245-4992</t>
+        </is>
+      </c>
       <c r="K16" s="12" t="n"/>
       <c r="L16" s="12" t="n"/>
       <c r="M16" s="11" t="inlineStr">
@@ -1373,12 +1381,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Andi Besse Kalsum</t>
+          <t>Abd. Mutalib</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1404,10 +1412,26 @@
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="11" t="n"/>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Andi Besse Kalsum</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Equine Breeding, Development and Sustainability Research Group focuses on the breeding, development, and sustainable utilization of equine livestock. Its research covers reproduction and breeding technologies, feed and nutrition, animal health, management and governance, socio-economic analysis, and tourism development. By integrating these aspects, the group aims to create an efficient, sustainable, and impactful horse farming model for the wider community.</t>
+        </is>
+      </c>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
@@ -1415,7 +1439,11 @@
       <c r="J18" s="12" t="n"/>
       <c r="K18" s="12" t="n"/>
       <c r="L18" s="12" t="n"/>
-      <c r="M18" s="12" t="n"/>
+      <c r="M18" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1604,15 +1632,32 @@
       <c r="L29" s="12" t="n"/>
       <c r="M29" s="12" t="n"/>
     </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="12" t="n"/>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="12" t="n"/>
+      <c r="J30" s="12" t="n"/>
+      <c r="K30" s="12" t="n"/>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
